--- a/data/2026/slides2026.xlsx
+++ b/data/2026/slides2026.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\efspieurope\workshop\data\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22F83801-6C80-4291-8494-1A69B789AFF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06B24894-3235-4665-A2D7-86A37E17255D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19490" yWindow="340" windowWidth="18250" windowHeight="19700" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tabelle1!$A$1:$F$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tabelle1!$A$1:$F$38</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="125">
   <si>
     <t>Session</t>
   </si>
@@ -279,15 +279,6 @@
   </si>
   <si>
     <t>Session 8</t>
-  </si>
-  <si>
-    <t>Theresa Stadler (Swiss Data Science Center, CH) and Matthias Templ (Fachhochschule Nordwestschweiz, CH)</t>
-  </si>
-  <si>
-    <t>What’s new about synthetic data? Promise, hype, and practical reality</t>
-  </si>
-  <si>
-    <t>08_Stadler.pdf</t>
   </si>
   <si>
     <t>Use of synthetic data in clinical trials: overcoming limitations of standard clinical trials</t>
@@ -806,18 +797,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:F39"/>
-  <sheetFormatPr defaultColWidth="136.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:F38"/>
+  <sheetFormatPr defaultColWidth="136.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.54296875" customWidth="1"/>
-    <col min="4" max="4" width="28.6328125" customWidth="1"/>
-    <col min="5" max="5" width="22.81640625" customWidth="1"/>
-    <col min="6" max="6" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.5703125" customWidth="1"/>
+    <col min="4" max="4" width="96.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -837,7 +828,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="25" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -854,10 +845,10 @@
         <v>9</v>
       </c>
       <c r="F2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -877,7 +868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -897,7 +888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
@@ -917,7 +908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -937,7 +928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -957,7 +948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="37.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" ht="38.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -977,7 +968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="25" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -997,7 +988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="50" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -1017,7 +1008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>35</v>
       </c>
@@ -1037,7 +1028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" ht="38.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>35</v>
       </c>
@@ -1057,7 +1048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="25" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>35</v>
       </c>
@@ -1077,7 +1068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>45</v>
       </c>
@@ -1097,7 +1088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="37.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" ht="38.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>45</v>
       </c>
@@ -1117,7 +1108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" ht="51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>52</v>
       </c>
@@ -1137,7 +1128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="37.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" ht="38.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>52</v>
       </c>
@@ -1157,7 +1148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>52</v>
       </c>
@@ -1177,7 +1168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>62</v>
       </c>
@@ -1197,7 +1188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" ht="38.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>62</v>
       </c>
@@ -1214,10 +1205,10 @@
         <v>68</v>
       </c>
       <c r="F20" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="25" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>62</v>
       </c>
@@ -1234,10 +1225,10 @@
         <v>71</v>
       </c>
       <c r="F21" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="37.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="38.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>72</v>
       </c>
@@ -1257,7 +1248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="37.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" ht="38.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>72</v>
       </c>
@@ -1277,7 +1268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" ht="38.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>79</v>
       </c>
@@ -1285,19 +1276,19 @@
         <v>1</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="F24" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="37.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="38.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>79</v>
       </c>
@@ -1305,44 +1296,44 @@
         <v>2</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="1">
+        <v>1</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="F25" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="37.5" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B26" s="1">
-        <v>3</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="E26" s="2" t="s">
-        <v>127</v>
+        <v>85</v>
       </c>
       <c r="F26" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="25" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B27" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>86</v>
@@ -1357,12 +1348,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="25" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" ht="38.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B28" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>89</v>
@@ -1374,15 +1365,15 @@
         <v>91</v>
       </c>
       <c r="F28" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="25" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="38.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B29" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>92</v>
@@ -1394,15 +1385,15 @@
         <v>94</v>
       </c>
       <c r="F29" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B30" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>95</v>
@@ -1417,12 +1408,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B31" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>98</v>
@@ -1437,12 +1428,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B32" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>101</v>
@@ -1457,12 +1448,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" ht="38.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B33" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>104</v>
@@ -1474,15 +1465,15 @@
         <v>106</v>
       </c>
       <c r="F33" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B34" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>107</v>
@@ -1494,15 +1485,15 @@
         <v>109</v>
       </c>
       <c r="F34" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="25" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B35" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>110</v>
@@ -1517,12 +1508,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B36" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>113</v>
@@ -1534,15 +1525,15 @@
         <v>115</v>
       </c>
       <c r="F36" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="25" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B37" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>116</v>
@@ -1557,12 +1548,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B38" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>119</v>
@@ -1577,28 +1568,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="50" x14ac:dyDescent="0.35">
-      <c r="A39" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B39" s="1">
-        <v>13</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F39" s="1">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F39" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:F38" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="5">
       <filters>
         <filter val="0"/>

--- a/data/2026/slides2026.xlsx
+++ b/data/2026/slides2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\efspieurope\workshop\data\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06B24894-3235-4665-A2D7-86A37E17255D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01D65B56-EF38-45E7-98F1-8D6D0D40CB59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -798,17 +798,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:F38"/>
-  <sheetFormatPr defaultColWidth="136.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="136.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.5703125" customWidth="1"/>
-    <col min="4" max="4" width="96.7109375" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.54296875" customWidth="1"/>
+    <col min="4" max="4" width="96.7265625" customWidth="1"/>
+    <col min="5" max="5" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -828,7 +828,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -848,7 +848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -868,7 +868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -888,7 +888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
@@ -908,7 +908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -928,7 +928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -948,7 +948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="38.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -968,7 +968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -988,7 +988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="50" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -1008,7 +1008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>35</v>
       </c>
@@ -1028,7 +1028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="38.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>35</v>
       </c>
@@ -1048,7 +1048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>35</v>
       </c>
@@ -1065,10 +1065,10 @@
         <v>44</v>
       </c>
       <c r="F13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>45</v>
       </c>
@@ -1088,7 +1088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="38.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>45</v>
       </c>
@@ -1108,7 +1108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>52</v>
       </c>
@@ -1128,7 +1128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="38.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>52</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>52</v>
       </c>
@@ -1168,7 +1168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>62</v>
       </c>
@@ -1185,10 +1185,10 @@
         <v>65</v>
       </c>
       <c r="F19" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="38.25" hidden="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>62</v>
       </c>
@@ -1208,7 +1208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>62</v>
       </c>
@@ -1228,7 +1228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="38.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>72</v>
       </c>
@@ -1248,7 +1248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="38.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>72</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="38.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>79</v>
       </c>
@@ -1288,7 +1288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="38.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>79</v>
       </c>
@@ -1308,7 +1308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>82</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>82</v>
       </c>
@@ -1348,7 +1348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="38.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>82</v>
       </c>
@@ -1368,7 +1368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="38.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>82</v>
       </c>
@@ -1388,7 +1388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>82</v>
       </c>
@@ -1408,7 +1408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>82</v>
       </c>
@@ -1428,7 +1428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>82</v>
       </c>
@@ -1448,7 +1448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="38.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>82</v>
       </c>
@@ -1468,7 +1468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>82</v>
       </c>
@@ -1488,7 +1488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>82</v>
       </c>
@@ -1508,7 +1508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>82</v>
       </c>
@@ -1528,7 +1528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>82</v>
       </c>
@@ -1548,7 +1548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="50" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>82</v>
       </c>

--- a/data/2026/slides2026.xlsx
+++ b/data/2026/slides2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\efspieurope\workshop\data\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01D65B56-EF38-45E7-98F1-8D6D0D40CB59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9812B97C-D791-4AA7-842B-5E9AC6AD8C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -332,9 +332,6 @@
     <t>Working together to shape the future of evidence for HTA and JCA</t>
   </si>
   <si>
-    <t>Poster_Allignol.pdf</t>
-  </si>
-  <si>
     <t>Orlando Dohring, Rima Izem, Min-Hua Jen, Iftekhar Khan, Josephine Wolfram</t>
   </si>
   <si>
@@ -404,9 +401,6 @@
     <t>EFSPI Scientific &amp; Training Academy</t>
   </si>
   <si>
-    <t>Poster_Bottigliengo.pdf</t>
-  </si>
-  <si>
     <t>Andrea Manfrin (MHRA, UK)</t>
   </si>
   <si>
@@ -414,6 +408,12 @@
   </si>
   <si>
     <t>08_Brizzi.pdf</t>
+  </si>
+  <si>
+    <t>Poster_Krebs.pdf</t>
+  </si>
+  <si>
+    <t>Poster_Badhan.pdf</t>
   </si>
 </sst>
 </file>
@@ -804,7 +804,7 @@
     <col min="2" max="2" width="11.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.54296875" customWidth="1"/>
     <col min="4" max="4" width="96.7265625" customWidth="1"/>
-    <col min="5" max="5" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="43.90625" customWidth="1"/>
     <col min="6" max="6" width="12.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1276,7 +1276,7 @@
         <v>1</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>80</v>
@@ -1296,19 +1296,19 @@
         <v>2</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>80</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F25" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>82</v>
       </c>
@@ -1325,7 +1325,7 @@
         <v>85</v>
       </c>
       <c r="F26" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
@@ -1388,7 +1388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="25" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>82</v>
       </c>
@@ -1402,13 +1402,13 @@
         <v>96</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="F30" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="25" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>82</v>
       </c>
@@ -1416,19 +1416,19 @@
         <v>6</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="E31" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="F31" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="25" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>82</v>
       </c>
@@ -1436,13 +1436,13 @@
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="E32" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -1456,13 +1456,13 @@
         <v>8</v>
       </c>
       <c r="C33" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="E33" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="F33" s="1">
         <v>1</v>
@@ -1476,13 +1476,13 @@
         <v>9</v>
       </c>
       <c r="C34" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="E34" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>109</v>
       </c>
       <c r="F34" s="1">
         <v>1</v>
@@ -1496,13 +1496,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="E35" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>112</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -1516,13 +1516,13 @@
         <v>11</v>
       </c>
       <c r="C36" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="E36" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>115</v>
       </c>
       <c r="F36" s="1">
         <v>1</v>
@@ -1536,19 +1536,19 @@
         <v>12</v>
       </c>
       <c r="C37" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="E37" s="2" t="s">
         <v>117</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>118</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="50" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>82</v>
       </c>
@@ -1556,16 +1556,16 @@
         <v>13</v>
       </c>
       <c r="C38" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="E38" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F38" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
